--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floswald/.julia/dev/JPEtools/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floswald/git/JPEtemplate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957E4354-791A-4942-ABF7-9C88724FEAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067DD2C7-24FE-2447-A5A8-8F6542C7C06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="21900" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
@@ -449,7 +449,7 @@
     <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -459,46 +459,50 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
